--- a/data/processed/harmonization/Carbon__Mineral-associated_organic_matter_carbon/harmonized.xlsx
+++ b/data/processed/harmonization/Carbon__Mineral-associated_organic_matter_carbon/harmonized.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:18</t>
+          <t>ER-MCB1:30:18</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:44</t>
+          <t>ER-MCB1:30:44</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:60</t>
+          <t>ER-MCB1:30:60</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:31</t>
+          <t>ER-MCB2:30:31</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:36</t>
+          <t>ER-MCB2:30:36</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:43</t>
+          <t>ER-MCB2:30:43</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:20</t>
+          <t>ER-MCB3:30:20</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:21</t>
+          <t>ER-MCB3:30:21</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:25</t>
+          <t>ER-MCB3:30:25</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:28</t>
+          <t>ER-MCB1:70:28</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:49</t>
+          <t>ER-MCB1:70:49</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:65</t>
+          <t>ER-MCB1:70:65</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:46</t>
+          <t>ER-MCB2:70:46</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:50</t>
+          <t>ER-MCB2:70:50</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:52</t>
+          <t>ER-MCB2:70:52</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:17</t>
+          <t>ER-MCB3:70:17</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:27</t>
+          <t>ER-MCB3:70:27</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:55</t>
+          <t>ER-MCB3:70:55</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3766,12 +3766,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
